--- a/new-info50/web.xlsx
+++ b/new-info50/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="12600" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>domain</t>
   </si>
@@ -40,34 +40,22 @@
     <t>color2</t>
   </si>
   <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>necrosia.cloud</t>
+  </si>
+  <si>
+    <t>#ae1c31</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
     <t>info</t>
   </si>
   <si>
     <t>json</t>
-  </si>
-  <si>
-    <t>read.mousseline.cloud</t>
-  </si>
-  <si>
-    <t>#ae1c31</t>
-  </si>
-  <si>
-    <t>sec.mousseline.cloud</t>
-  </si>
-  <si>
-    <t>fipples.fun</t>
-  </si>
-  <si>
-    <t>#4caf50</t>
-  </si>
-  <si>
-    <t>noctivag.fun</t>
-  </si>
-  <si>
-    <t>#606da1</t>
-  </si>
-  <si>
-    <t>color</t>
   </si>
   <si>
     <t>vernations.cloud</t>
@@ -149,7 +137,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -201,13 +189,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -359,7 +340,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="48">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -453,18 +434,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFAE1C31"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4CAF50"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF606DA1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -764,85 +733,91 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -851,10 +826,10 @@
     <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -863,10 +838,10 @@
     <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -875,10 +850,10 @@
     <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -887,10 +862,10 @@
     <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -899,17 +874,11 @@
     <xf numFmtId="0" fontId="26" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -962,25 +931,18 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1366,82 +1328,57 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="1" max="1" width="17.875" style="18" customWidth="1"/>
+    <col min="2" max="3" width="9" style="18"/>
+    <col min="4" max="4" width="10.375" style="18" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" t="s">
+    <row r="1" s="18" customFormat="1" spans="1:4">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" s="18" customFormat="1" spans="1:4">
+      <c r="A2" s="19" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="18" t="s">
+      <c r="B2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="24"/>
+      <c r="D2" s="21">
+        <v>46193</v>
+      </c>
+    </row>
+    <row r="3" s="18" customFormat="1" spans="1:4">
+      <c r="A3" s="22"/>
+      <c r="B3" s="20"/>
+    </row>
+    <row r="4" s="18" customFormat="1" spans="1:4">
+      <c r="A4" s="19"/>
+      <c r="B4" s="13"/>
+    </row>
+    <row r="5" s="18" customFormat="1" spans="1:4">
+      <c r="A5" s="23"/>
+      <c r="B5" s="14"/>
+    </row>
+    <row r="6" s="18" customFormat="1" spans="1:4">
+      <c r="A6" s="19"/>
       <c r="B6" s="15"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="read.mousseline.cloud"/>
-    <hyperlink ref="A3" r:id="rId1" display="sec.mousseline.cloud"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1461,24 +1398,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1489,10 +1426,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1503,10 +1440,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1517,10 +1454,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1531,10 +1468,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1545,18 +1482,18 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="16" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="16" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1596,49 +1533,49 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
